--- a/Customer_Payments_Tracker.xlsx
+++ b/Customer_Payments_Tracker.xlsx
@@ -20,13 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,7 +42,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="22"/>
+      <sz val="21"/>
     </font>
     <font>
       <i val="1"/>
@@ -51,25 +52,28 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="009C6500"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,22 +82,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="003B4758"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FC"/>
+        <fgColor rgb="00FDF3D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00C55A11"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,38 +108,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -232,7 +266,7 @@
       </tx>
     </title>
     <plotArea>
-      <pieChart>
+      <doughnutChart>
         <varyColors val="1"/>
         <ser>
           <idx val="0"/>
@@ -259,7 +293,8 @@
           </val>
         </ser>
         <firstSliceAng val="0"/>
-      </pieChart>
+        <holeSize val="55"/>
+      </doughnutChart>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -271,91 +306,6 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Invoiced Amount by Month</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Calc'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Calc'!$D$2:$D$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Calc'!$E$2:$E$10</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -434,7 +384,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -446,22 +396,21 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Invoice Count by Status</a:t>
+              <a:t>Invoiced by Month</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Calc'!K1</f>
+              <f>'Calc'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -469,21 +418,28 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
           <cat>
             <numRef>
-              <f>'Calc'!$J$2:$J$4</f>
+              <f>'Calc'!$D$2:$D$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Calc'!$K$2:$K$4</f>
+              <f>'Calc'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
-      </barChart>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -517,9 +473,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4680000" cy="2880000"/>
@@ -539,12 +495,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="2880000"/>
+    <ext cx="4320000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -561,12 +517,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="2880000"/>
+    <ext cx="4320000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -576,28 +532,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4680000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -892,11 +826,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="003B4758"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -917,7 +851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CUSTOMER PAYMENTS - A/R TRACKER 2026</t>
+          <t>💳  CUSTOMER PAYMENTS — COLLECTIONS CONTROL</t>
         </is>
       </c>
     </row>
@@ -925,110 +859,155 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Invoice tracking: collected vs outstanding vs overdue - all formula-driven</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
+          <t>Accounts receivable 2026 · collected vs outstanding vs overdue · status chips auto-colored in Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TOTAL INVOICED</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>COLLECTED</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>OUTSTANDING</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>OVERDUE AMOUNT</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="4">
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="4">
         <f>SUM(Data!F2:F121)</f>
         <v/>
       </c>
-      <c r="E5" s="4">
+      <c r="E6" s="4">
         <f>SUMIF(Data!G2:G121,"Paid",Data!F2:F121)</f>
         <v/>
       </c>
-      <c r="H5" s="4">
+      <c r="H6" s="4">
         <f>SUM(Data!F2:F121)-SUMIF(Data!G2:G121,"Paid",Data!F2:F121)</f>
         <v/>
       </c>
-      <c r="K5" s="4">
+      <c r="K6" s="4">
         <f>SUMIF(Data!G2:G121,"Overdue",Data!F2:F121)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>COLLECTION RATE</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>BIGGEST DEBTOR</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>AVG INVOICE</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>OVERDUE INVOICES</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="6">
-        <f>SUMIF(Data!G2:G121,"Paid",Data!F2:F121)/SUM(Data!F2:F121)</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>INDEX(Calc!G2:G9,MATCH(MAX(Calc!H2:H9),Calc!H2:H9,0))</f>
-        <v/>
-      </c>
-      <c r="H8" s="6">
-        <f>AVERAGE(Data!F2:F121)</f>
-        <v/>
-      </c>
-      <c r="K8" s="6">
-        <f>COUNTIF(Data!G2:G121,"Overdue")</f>
-        <v/>
-      </c>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>⏳  OVERDUE AGING</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>AGE BUCKET</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>AMOUNT</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>% OF OVERDUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10">
+        <f>Calc!M2</f>
+        <v/>
+      </c>
+      <c r="C10" s="7">
+        <f>Calc!N2</f>
+        <v/>
+      </c>
+      <c r="D10" s="8">
+        <f>IF(SUM(C10:C13)=0,0,C10/SUM(C$10:C$13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11">
+        <f>Calc!M3</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>Calc!N3</f>
+        <v/>
+      </c>
+      <c r="D11" s="8">
+        <f>IF(SUM(C10:C13)=0,0,C11/SUM(C$10:C$13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12">
+        <f>Calc!M4</f>
+        <v/>
+      </c>
+      <c r="C12" s="7">
+        <f>Calc!N4</f>
+        <v/>
+      </c>
+      <c r="D12" s="8">
+        <f>IF(SUM(C10:C13)=0,0,C12/SUM(C$10:C$13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13">
+        <f>Calc!M5</f>
+        <v/>
+      </c>
+      <c r="C13" s="7">
+        <f>Calc!N5</f>
+        <v/>
+      </c>
+      <c r="D13" s="8">
+        <f>IF(SUM(C10:C13)=0,0,C13/SUM(C$10:C$13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14" s="10">
+        <f>SUM(C10:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="H4:I4"/>
+  <mergeCells count="11">
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="H7:I7"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:N2"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A3:N3"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1038,6 +1017,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="003B4758"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1055,78 +1035,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Invoice No</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Issue Date</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Days Overdue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>INV-2026-001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="13" t="n">
         <v>46220</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="13" t="n">
         <v>46250</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="14" t="n">
         <v>1130.33</v>
       </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H2" s="8">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H2">
         <f>IF(G2="Overdue",DATE(2026,10,1)-E2,0)</f>
         <v/>
       </c>
@@ -1147,13 +1127,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="13" t="n">
         <v>46122</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="13" t="n">
         <v>46152</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="14" t="n">
         <v>2972.84</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -1167,36 +1147,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>INV-2026-003</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="13" t="n">
         <v>46059</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="13" t="n">
         <v>46089</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="14" t="n">
         <v>3559.5</v>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H4" s="8">
+      <c r="H4">
         <f>IF(G4="Overdue",DATE(2026,10,1)-E4,0)</f>
         <v/>
       </c>
@@ -1217,13 +1197,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="13" t="n">
         <v>46222</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="13" t="n">
         <v>46252</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="14" t="n">
         <v>1983.94</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -1237,36 +1217,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>INV-2026-005</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Gamma Retail</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="13" t="n">
         <v>46200</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="13" t="n">
         <v>46230</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="14" t="n">
         <v>826.45</v>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H6" s="8">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H6">
         <f>IF(G6="Overdue",DATE(2026,10,1)-E6,0)</f>
         <v/>
       </c>
@@ -1287,13 +1267,13 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="13" t="n">
         <v>46072</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="13" t="n">
         <v>46102</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="14" t="n">
         <v>806.27</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -1307,36 +1287,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>INV-2026-007</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="13" t="n">
         <v>46144</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="13" t="n">
         <v>46174</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="14" t="n">
         <v>2543.22</v>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H8" s="8">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H8">
         <f>IF(G8="Overdue",DATE(2026,10,1)-E8,0)</f>
         <v/>
       </c>
@@ -1357,13 +1337,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="13" t="n">
         <v>46119</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>46149</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="14" t="n">
         <v>3949.83</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -1377,36 +1357,36 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>INV-2026-009</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Eta Pharma</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="13" t="n">
         <v>46044</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="13" t="n">
         <v>46074</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="14" t="n">
         <v>3636.35</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H10" s="8">
+      <c r="H10">
         <f>IF(G10="Overdue",DATE(2026,10,1)-E10,0)</f>
         <v/>
       </c>
@@ -1427,13 +1407,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="13" t="n">
         <v>46185</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="13" t="n">
         <v>46215</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="14" t="n">
         <v>3072.88</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -1447,36 +1427,36 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>INV-2026-011</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="13" t="n">
         <v>46270</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="13" t="n">
         <v>46300</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="14" t="n">
         <v>4969.5</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H12">
         <f>IF(G12="Overdue",DATE(2026,10,1)-E12,0)</f>
         <v/>
       </c>
@@ -1497,13 +1477,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="13" t="n">
         <v>46193</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="13" t="n">
         <v>46223</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="14" t="n">
         <v>1606.46</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -1517,36 +1497,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>INV-2026-013</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="13" t="n">
         <v>46030</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="13" t="n">
         <v>46060</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="14" t="n">
         <v>4974.93</v>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H14" s="8">
+      <c r="H14">
         <f>IF(G14="Overdue",DATE(2026,10,1)-E14,0)</f>
         <v/>
       </c>
@@ -1567,13 +1547,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="13" t="n">
         <v>46192</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="13" t="n">
         <v>46222</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="14" t="n">
         <v>1996.43</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -1587,36 +1567,36 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>INV-2026-015</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Alfa Construct</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="13" t="n">
         <v>46080</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="13" t="n">
         <v>46110</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="14" t="n">
         <v>4994.92</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H16">
         <f>IF(G16="Overdue",DATE(2026,10,1)-E16,0)</f>
         <v/>
       </c>
@@ -1637,13 +1617,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="13" t="n">
         <v>46044</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="13" t="n">
         <v>46074</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="14" t="n">
         <v>970.61</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -1657,36 +1637,36 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>INV-2026-017</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="13" t="n">
         <v>46042</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="13" t="n">
         <v>46072</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="14" t="n">
         <v>1578.63</v>
       </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H18" s="8">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H18">
         <f>IF(G18="Overdue",DATE(2026,10,1)-E18,0)</f>
         <v/>
       </c>
@@ -1707,13 +1687,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="13" t="n">
         <v>46036</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="13" t="n">
         <v>46066</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="14" t="n">
         <v>4332.84</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -1727,36 +1707,36 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>INV-2026-019</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="13" t="n">
         <v>46031</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="13" t="n">
         <v>46061</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="14" t="n">
         <v>4875.83</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H20" s="8">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H20">
         <f>IF(G20="Overdue",DATE(2026,10,1)-E20,0)</f>
         <v/>
       </c>
@@ -1777,13 +1757,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="13" t="n">
         <v>46290</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="13" t="n">
         <v>46320</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="14" t="n">
         <v>2867.81</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -1797,36 +1777,36 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>INV-2026-021</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="13" t="n">
         <v>46237</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="13" t="n">
         <v>46267</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="14" t="n">
         <v>2185.46</v>
       </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H22" s="8">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H22">
         <f>IF(G22="Overdue",DATE(2026,10,1)-E22,0)</f>
         <v/>
       </c>
@@ -1847,13 +1827,13 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="13" t="n">
         <v>46160</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="13" t="n">
         <v>46190</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F23" s="14" t="n">
         <v>642.03</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -1867,36 +1847,36 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>INV-2026-023</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Gamma Retail</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="13" t="n">
         <v>46147</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="13" t="n">
         <v>46177</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="14" t="n">
         <v>649.49</v>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H24" s="8">
+      <c r="H24">
         <f>IF(G24="Overdue",DATE(2026,10,1)-E24,0)</f>
         <v/>
       </c>
@@ -1917,13 +1897,13 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="13" t="n">
         <v>46247</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="13" t="n">
         <v>46277</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="14" t="n">
         <v>695.87</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -1937,36 +1917,36 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>INV-2026-025</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="13" t="n">
         <v>46090</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="13" t="n">
         <v>46120</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="14" t="n">
         <v>1442.72</v>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H26" s="8">
+      <c r="H26">
         <f>IF(G26="Overdue",DATE(2026,10,1)-E26,0)</f>
         <v/>
       </c>
@@ -1987,13 +1967,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="13" t="n">
         <v>46130</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="13" t="n">
         <v>46160</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="14" t="n">
         <v>4361.69</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -2007,36 +1987,36 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>INV-2026-027</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="13" t="n">
         <v>46096</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="13" t="n">
         <v>46126</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="14" t="n">
         <v>4649.84</v>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H28" s="8">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H28">
         <f>IF(G28="Overdue",DATE(2026,10,1)-E28,0)</f>
         <v/>
       </c>
@@ -2057,13 +2037,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="13" t="n">
         <v>46190</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="13" t="n">
         <v>46220</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="14" t="n">
         <v>4592.67</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -2077,36 +2057,36 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>INV-2026-029</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Eta Pharma</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="13" t="n">
         <v>46082</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="13" t="n">
         <v>46112</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="14" t="n">
         <v>4708.6</v>
       </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H30" s="8">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H30">
         <f>IF(G30="Overdue",DATE(2026,10,1)-E30,0)</f>
         <v/>
       </c>
@@ -2127,13 +2107,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="13" t="n">
         <v>46216</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="13" t="n">
         <v>46246</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="14" t="n">
         <v>1332.67</v>
       </c>
       <c r="G31" t="inlineStr">
@@ -2147,36 +2127,36 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>INV-2026-031</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Alfa Construct</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="13" t="n">
         <v>46104</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="13" t="n">
         <v>46134</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="14" t="n">
         <v>1868.66</v>
       </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H32" s="8">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H32">
         <f>IF(G32="Overdue",DATE(2026,10,1)-E32,0)</f>
         <v/>
       </c>
@@ -2197,13 +2177,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="13" t="n">
         <v>46040</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="13" t="n">
         <v>46070</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="14" t="n">
         <v>1082.8</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -2217,36 +2197,36 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>INV-2026-033</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="13" t="n">
         <v>46266</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="13" t="n">
         <v>46296</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="14" t="n">
         <v>2139.47</v>
       </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H34" s="8">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H34">
         <f>IF(G34="Overdue",DATE(2026,10,1)-E34,0)</f>
         <v/>
       </c>
@@ -2267,13 +2247,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="13" t="n">
         <v>46267</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="13" t="n">
         <v>46297</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="14" t="n">
         <v>2193.29</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -2287,36 +2267,36 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>INV-2026-035</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="13" t="n">
         <v>46169</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="13" t="n">
         <v>46199</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="14" t="n">
         <v>1812.6</v>
       </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H36" s="8">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H36">
         <f>IF(G36="Overdue",DATE(2026,10,1)-E36,0)</f>
         <v/>
       </c>
@@ -2337,13 +2317,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="13" t="n">
         <v>46194</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="13" t="n">
         <v>46224</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F37" s="14" t="n">
         <v>376.64</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -2357,36 +2337,36 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>INV-2026-037</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Gamma Retail</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="13" t="n">
         <v>46116</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="13" t="n">
         <v>46146</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="14" t="n">
         <v>653.77</v>
       </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H38" s="8">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H38">
         <f>IF(G38="Overdue",DATE(2026,10,1)-E38,0)</f>
         <v/>
       </c>
@@ -2407,13 +2387,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="13" t="n">
         <v>46269</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="13" t="n">
         <v>46299</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="14" t="n">
         <v>4511.98</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -2427,36 +2407,36 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>INV-2026-039</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="13" t="n">
         <v>46155</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="13" t="n">
         <v>46185</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="14" t="n">
         <v>3051.01</v>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H40" s="8">
+      <c r="H40">
         <f>IF(G40="Overdue",DATE(2026,10,1)-E40,0)</f>
         <v/>
       </c>
@@ -2477,13 +2457,13 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="13" t="n">
         <v>46091</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="13" t="n">
         <v>46121</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="14" t="n">
         <v>3911.07</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -2497,36 +2477,36 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>INV-2026-041</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="13" t="n">
         <v>46103</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="13" t="n">
         <v>46133</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="14" t="n">
         <v>1139.98</v>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H42" s="8">
+      <c r="H42">
         <f>IF(G42="Overdue",DATE(2026,10,1)-E42,0)</f>
         <v/>
       </c>
@@ -2547,13 +2527,13 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="13" t="n">
         <v>46250</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F43" s="14" t="n">
         <v>3537.08</v>
       </c>
       <c r="G43" t="inlineStr">
@@ -2567,36 +2547,36 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>INV-2026-043</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" s="13" t="n">
         <v>46250</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="13" t="n">
         <v>46280</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="14" t="n">
         <v>2450.76</v>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H44" s="8">
+      <c r="H44">
         <f>IF(G44="Overdue",DATE(2026,10,1)-E44,0)</f>
         <v/>
       </c>
@@ -2617,13 +2597,13 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="13" t="n">
         <v>46161</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="13" t="n">
         <v>46191</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F45" s="14" t="n">
         <v>2557.56</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -2637,36 +2617,36 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>INV-2026-045</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="13" t="n">
         <v>46093</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="13" t="n">
         <v>46123</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="14" t="n">
         <v>2295.52</v>
       </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H46" s="8">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H46">
         <f>IF(G46="Overdue",DATE(2026,10,1)-E46,0)</f>
         <v/>
       </c>
@@ -2687,13 +2667,13 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="13" t="n">
         <v>46144</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="13" t="n">
         <v>46174</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F47" s="14" t="n">
         <v>757.48</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -2707,36 +2687,36 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>INV-2026-047</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Alfa Construct</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D48" s="9" t="n">
+      <c r="D48" s="13" t="n">
         <v>46138</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="13" t="n">
         <v>46168</v>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="14" t="n">
         <v>1112.18</v>
       </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H48" s="8">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H48">
         <f>IF(G48="Overdue",DATE(2026,10,1)-E48,0)</f>
         <v/>
       </c>
@@ -2757,13 +2737,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="13" t="n">
         <v>46134</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="13" t="n">
         <v>46164</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="F49" s="14" t="n">
         <v>2385.14</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -2777,36 +2757,36 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>INV-2026-049</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="D50" s="13" t="n">
         <v>46041</v>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="E50" s="13" t="n">
         <v>46071</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="14" t="n">
         <v>1090.13</v>
       </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H50" s="8">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H50">
         <f>IF(G50="Overdue",DATE(2026,10,1)-E50,0)</f>
         <v/>
       </c>
@@ -2827,13 +2807,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="13" t="n">
         <v>46137</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E51" s="13" t="n">
         <v>46167</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F51" s="14" t="n">
         <v>4730.51</v>
       </c>
       <c r="G51" t="inlineStr">
@@ -2847,36 +2827,36 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>INV-2026-051</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="D52" s="13" t="n">
         <v>46083</v>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="E52" s="13" t="n">
         <v>46113</v>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="14" t="n">
         <v>528.11</v>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H52" s="8">
+      <c r="H52">
         <f>IF(G52="Overdue",DATE(2026,10,1)-E52,0)</f>
         <v/>
       </c>
@@ -2897,13 +2877,13 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="13" t="n">
         <v>46063</v>
       </c>
-      <c r="E53" s="11" t="n">
+      <c r="E53" s="13" t="n">
         <v>46093</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="F53" s="14" t="n">
         <v>2370.21</v>
       </c>
       <c r="G53" t="inlineStr">
@@ -2917,36 +2897,36 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>INV-2026-053</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D54" s="9" t="n">
+      <c r="D54" s="13" t="n">
         <v>46030</v>
       </c>
-      <c r="E54" s="9" t="n">
+      <c r="E54" s="13" t="n">
         <v>46060</v>
       </c>
-      <c r="F54" s="10" t="n">
+      <c r="F54" s="14" t="n">
         <v>662.85</v>
       </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H54" s="8">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H54">
         <f>IF(G54="Overdue",DATE(2026,10,1)-E54,0)</f>
         <v/>
       </c>
@@ -2967,13 +2947,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D55" s="11" t="n">
+      <c r="D55" s="13" t="n">
         <v>46024</v>
       </c>
-      <c r="E55" s="11" t="n">
+      <c r="E55" s="13" t="n">
         <v>46054</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="F55" s="14" t="n">
         <v>4213.98</v>
       </c>
       <c r="G55" t="inlineStr">
@@ -2987,36 +2967,36 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>INV-2026-055</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D56" s="9" t="n">
+      <c r="D56" s="13" t="n">
         <v>46238</v>
       </c>
-      <c r="E56" s="9" t="n">
+      <c r="E56" s="13" t="n">
         <v>46268</v>
       </c>
-      <c r="F56" s="10" t="n">
+      <c r="F56" s="14" t="n">
         <v>2410.35</v>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H56" s="8">
+      <c r="H56">
         <f>IF(G56="Overdue",DATE(2026,10,1)-E56,0)</f>
         <v/>
       </c>
@@ -3037,13 +3017,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D57" s="13" t="n">
         <v>46281</v>
       </c>
-      <c r="E57" s="11" t="n">
+      <c r="E57" s="13" t="n">
         <v>46311</v>
       </c>
-      <c r="F57" s="12" t="n">
+      <c r="F57" s="14" t="n">
         <v>2136.5</v>
       </c>
       <c r="G57" t="inlineStr">
@@ -3057,36 +3037,36 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>INV-2026-057</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D58" s="9" t="n">
+      <c r="D58" s="13" t="n">
         <v>46286</v>
       </c>
-      <c r="E58" s="9" t="n">
+      <c r="E58" s="13" t="n">
         <v>46316</v>
       </c>
-      <c r="F58" s="10" t="n">
+      <c r="F58" s="14" t="n">
         <v>3265.69</v>
       </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H58" s="8">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H58">
         <f>IF(G58="Overdue",DATE(2026,10,1)-E58,0)</f>
         <v/>
       </c>
@@ -3107,13 +3087,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D59" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E59" s="13" t="n">
         <v>46309</v>
       </c>
-      <c r="F59" s="12" t="n">
+      <c r="F59" s="14" t="n">
         <v>2127.2</v>
       </c>
       <c r="G59" t="inlineStr">
@@ -3127,36 +3107,36 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>INV-2026-059</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D60" s="9" t="n">
+      <c r="D60" s="13" t="n">
         <v>46287</v>
       </c>
-      <c r="E60" s="9" t="n">
+      <c r="E60" s="13" t="n">
         <v>46317</v>
       </c>
-      <c r="F60" s="10" t="n">
+      <c r="F60" s="14" t="n">
         <v>4921.45</v>
       </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H60" s="8">
+      <c r="H60">
         <f>IF(G60="Overdue",DATE(2026,10,1)-E60,0)</f>
         <v/>
       </c>
@@ -3177,13 +3157,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D61" s="13" t="n">
         <v>46278</v>
       </c>
-      <c r="E61" s="11" t="n">
+      <c r="E61" s="13" t="n">
         <v>46308</v>
       </c>
-      <c r="F61" s="12" t="n">
+      <c r="F61" s="14" t="n">
         <v>1276.36</v>
       </c>
       <c r="G61" t="inlineStr">
@@ -3197,36 +3177,36 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>INV-2026-061</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D62" s="9" t="n">
+      <c r="D62" s="13" t="n">
         <v>46151</v>
       </c>
-      <c r="E62" s="9" t="n">
+      <c r="E62" s="13" t="n">
         <v>46181</v>
       </c>
-      <c r="F62" s="10" t="n">
+      <c r="F62" s="14" t="n">
         <v>701.55</v>
       </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H62" s="8">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H62">
         <f>IF(G62="Overdue",DATE(2026,10,1)-E62,0)</f>
         <v/>
       </c>
@@ -3247,13 +3227,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="13" t="n">
         <v>46278</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E63" s="13" t="n">
         <v>46308</v>
       </c>
-      <c r="F63" s="12" t="n">
+      <c r="F63" s="14" t="n">
         <v>1860.59</v>
       </c>
       <c r="G63" t="inlineStr">
@@ -3267,36 +3247,36 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>INV-2026-063</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D64" s="9" t="n">
+      <c r="D64" s="13" t="n">
         <v>46204</v>
       </c>
-      <c r="E64" s="9" t="n">
+      <c r="E64" s="13" t="n">
         <v>46234</v>
       </c>
-      <c r="F64" s="10" t="n">
+      <c r="F64" s="14" t="n">
         <v>2180.49</v>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H64" s="8">
+      <c r="H64">
         <f>IF(G64="Overdue",DATE(2026,10,1)-E64,0)</f>
         <v/>
       </c>
@@ -3317,13 +3297,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D65" s="11" t="n">
+      <c r="D65" s="13" t="n">
         <v>46035</v>
       </c>
-      <c r="E65" s="11" t="n">
+      <c r="E65" s="13" t="n">
         <v>46065</v>
       </c>
-      <c r="F65" s="12" t="n">
+      <c r="F65" s="14" t="n">
         <v>3862.81</v>
       </c>
       <c r="G65" t="inlineStr">
@@ -3337,36 +3317,36 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>INV-2026-065</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D66" s="9" t="n">
+      <c r="D66" s="13" t="n">
         <v>46187</v>
       </c>
-      <c r="E66" s="9" t="n">
+      <c r="E66" s="13" t="n">
         <v>46217</v>
       </c>
-      <c r="F66" s="10" t="n">
+      <c r="F66" s="14" t="n">
         <v>4425.73</v>
       </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H66" s="8">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H66">
         <f>IF(G66="Overdue",DATE(2026,10,1)-E66,0)</f>
         <v/>
       </c>
@@ -3387,13 +3367,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D67" s="13" t="n">
         <v>46214</v>
       </c>
-      <c r="E67" s="11" t="n">
+      <c r="E67" s="13" t="n">
         <v>46244</v>
       </c>
-      <c r="F67" s="12" t="n">
+      <c r="F67" s="14" t="n">
         <v>3063.19</v>
       </c>
       <c r="G67" t="inlineStr">
@@ -3407,36 +3387,36 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>INV-2026-067</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D68" s="9" t="n">
+      <c r="D68" s="13" t="n">
         <v>46108</v>
       </c>
-      <c r="E68" s="9" t="n">
+      <c r="E68" s="13" t="n">
         <v>46138</v>
       </c>
-      <c r="F68" s="10" t="n">
+      <c r="F68" s="14" t="n">
         <v>3653.71</v>
       </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H68" s="8">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H68">
         <f>IF(G68="Overdue",DATE(2026,10,1)-E68,0)</f>
         <v/>
       </c>
@@ -3457,13 +3437,13 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D69" s="11" t="n">
+      <c r="D69" s="13" t="n">
         <v>46062</v>
       </c>
-      <c r="E69" s="11" t="n">
+      <c r="E69" s="13" t="n">
         <v>46092</v>
       </c>
-      <c r="F69" s="12" t="n">
+      <c r="F69" s="14" t="n">
         <v>2966.8</v>
       </c>
       <c r="G69" t="inlineStr">
@@ -3477,36 +3457,36 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>INV-2026-069</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D70" s="9" t="n">
+      <c r="D70" s="13" t="n">
         <v>46272</v>
       </c>
-      <c r="E70" s="9" t="n">
+      <c r="E70" s="13" t="n">
         <v>46302</v>
       </c>
-      <c r="F70" s="10" t="n">
+      <c r="F70" s="14" t="n">
         <v>4941.09</v>
       </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H70" s="8">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H70">
         <f>IF(G70="Overdue",DATE(2026,10,1)-E70,0)</f>
         <v/>
       </c>
@@ -3527,13 +3507,13 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D71" s="11" t="n">
+      <c r="D71" s="13" t="n">
         <v>46244</v>
       </c>
-      <c r="E71" s="11" t="n">
+      <c r="E71" s="13" t="n">
         <v>46274</v>
       </c>
-      <c r="F71" s="12" t="n">
+      <c r="F71" s="14" t="n">
         <v>1831.11</v>
       </c>
       <c r="G71" t="inlineStr">
@@ -3547,36 +3527,36 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>INV-2026-071</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D72" s="9" t="n">
+      <c r="D72" s="13" t="n">
         <v>46143</v>
       </c>
-      <c r="E72" s="9" t="n">
+      <c r="E72" s="13" t="n">
         <v>46173</v>
       </c>
-      <c r="F72" s="10" t="n">
+      <c r="F72" s="14" t="n">
         <v>2246.4</v>
       </c>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H72" s="8">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H72">
         <f>IF(G72="Overdue",DATE(2026,10,1)-E72,0)</f>
         <v/>
       </c>
@@ -3597,13 +3577,13 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="13" t="n">
         <v>46252</v>
       </c>
-      <c r="E73" s="11" t="n">
+      <c r="E73" s="13" t="n">
         <v>46282</v>
       </c>
-      <c r="F73" s="12" t="n">
+      <c r="F73" s="14" t="n">
         <v>3147.54</v>
       </c>
       <c r="G73" t="inlineStr">
@@ -3617,36 +3597,36 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>INV-2026-073</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D74" s="9" t="n">
+      <c r="D74" s="13" t="n">
         <v>46135</v>
       </c>
-      <c r="E74" s="9" t="n">
+      <c r="E74" s="13" t="n">
         <v>46165</v>
       </c>
-      <c r="F74" s="10" t="n">
+      <c r="F74" s="14" t="n">
         <v>2580.35</v>
       </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H74" s="8">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H74">
         <f>IF(G74="Overdue",DATE(2026,10,1)-E74,0)</f>
         <v/>
       </c>
@@ -3667,13 +3647,13 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D75" s="11" t="n">
+      <c r="D75" s="13" t="n">
         <v>46161</v>
       </c>
-      <c r="E75" s="11" t="n">
+      <c r="E75" s="13" t="n">
         <v>46191</v>
       </c>
-      <c r="F75" s="12" t="n">
+      <c r="F75" s="14" t="n">
         <v>1716.02</v>
       </c>
       <c r="G75" t="inlineStr">
@@ -3687,36 +3667,36 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>INV-2026-075</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Alfa Construct</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D76" s="9" t="n">
+      <c r="D76" s="13" t="n">
         <v>46285</v>
       </c>
-      <c r="E76" s="9" t="n">
+      <c r="E76" s="13" t="n">
         <v>46315</v>
       </c>
-      <c r="F76" s="10" t="n">
+      <c r="F76" s="14" t="n">
         <v>2050.55</v>
       </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H76" s="8">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H76">
         <f>IF(G76="Overdue",DATE(2026,10,1)-E76,0)</f>
         <v/>
       </c>
@@ -3737,13 +3717,13 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D77" s="11" t="n">
+      <c r="D77" s="13" t="n">
         <v>46055</v>
       </c>
-      <c r="E77" s="11" t="n">
+      <c r="E77" s="13" t="n">
         <v>46085</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="F77" s="14" t="n">
         <v>2750.06</v>
       </c>
       <c r="G77" t="inlineStr">
@@ -3757,36 +3737,36 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>INV-2026-077</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D78" s="9" t="n">
+      <c r="D78" s="13" t="n">
         <v>46221</v>
       </c>
-      <c r="E78" s="9" t="n">
+      <c r="E78" s="13" t="n">
         <v>46251</v>
       </c>
-      <c r="F78" s="10" t="n">
+      <c r="F78" s="14" t="n">
         <v>1947.43</v>
       </c>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H78" s="8">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H78">
         <f>IF(G78="Overdue",DATE(2026,10,1)-E78,0)</f>
         <v/>
       </c>
@@ -3807,13 +3787,13 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D79" s="13" t="n">
         <v>46082</v>
       </c>
-      <c r="E79" s="11" t="n">
+      <c r="E79" s="13" t="n">
         <v>46112</v>
       </c>
-      <c r="F79" s="12" t="n">
+      <c r="F79" s="14" t="n">
         <v>2605.23</v>
       </c>
       <c r="G79" t="inlineStr">
@@ -3827,36 +3807,36 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>INV-2026-079</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D80" s="9" t="n">
+      <c r="D80" s="13" t="n">
         <v>46205</v>
       </c>
-      <c r="E80" s="9" t="n">
+      <c r="E80" s="13" t="n">
         <v>46235</v>
       </c>
-      <c r="F80" s="10" t="n">
+      <c r="F80" s="14" t="n">
         <v>300.22</v>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H80" s="8">
+      <c r="H80">
         <f>IF(G80="Overdue",DATE(2026,10,1)-E80,0)</f>
         <v/>
       </c>
@@ -3877,13 +3857,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="13" t="n">
         <v>46224</v>
       </c>
-      <c r="E81" s="11" t="n">
+      <c r="E81" s="13" t="n">
         <v>46254</v>
       </c>
-      <c r="F81" s="12" t="n">
+      <c r="F81" s="14" t="n">
         <v>1173.66</v>
       </c>
       <c r="G81" t="inlineStr">
@@ -3897,36 +3877,36 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>INV-2026-081</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D82" s="9" t="n">
+      <c r="D82" s="13" t="n">
         <v>46255</v>
       </c>
-      <c r="E82" s="9" t="n">
+      <c r="E82" s="13" t="n">
         <v>46285</v>
       </c>
-      <c r="F82" s="10" t="n">
+      <c r="F82" s="14" t="n">
         <v>1745.24</v>
       </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H82" s="8">
+      <c r="H82">
         <f>IF(G82="Overdue",DATE(2026,10,1)-E82,0)</f>
         <v/>
       </c>
@@ -3947,13 +3927,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D83" s="11" t="n">
+      <c r="D83" s="13" t="n">
         <v>46049</v>
       </c>
-      <c r="E83" s="11" t="n">
+      <c r="E83" s="13" t="n">
         <v>46079</v>
       </c>
-      <c r="F83" s="12" t="n">
+      <c r="F83" s="14" t="n">
         <v>4333.82</v>
       </c>
       <c r="G83" t="inlineStr">
@@ -3967,36 +3947,36 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>INV-2026-083</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D84" s="9" t="n">
+      <c r="D84" s="13" t="n">
         <v>46156</v>
       </c>
-      <c r="E84" s="9" t="n">
+      <c r="E84" s="13" t="n">
         <v>46186</v>
       </c>
-      <c r="F84" s="10" t="n">
+      <c r="F84" s="14" t="n">
         <v>373.1</v>
       </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H84" s="8">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H84">
         <f>IF(G84="Overdue",DATE(2026,10,1)-E84,0)</f>
         <v/>
       </c>
@@ -4017,13 +3997,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D85" s="11" t="n">
+      <c r="D85" s="13" t="n">
         <v>46116</v>
       </c>
-      <c r="E85" s="11" t="n">
+      <c r="E85" s="13" t="n">
         <v>46146</v>
       </c>
-      <c r="F85" s="12" t="n">
+      <c r="F85" s="14" t="n">
         <v>2083.29</v>
       </c>
       <c r="G85" t="inlineStr">
@@ -4037,36 +4017,36 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>INV-2026-085</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D86" s="9" t="n">
+      <c r="D86" s="13" t="n">
         <v>46287</v>
       </c>
-      <c r="E86" s="9" t="n">
+      <c r="E86" s="13" t="n">
         <v>46317</v>
       </c>
-      <c r="F86" s="10" t="n">
+      <c r="F86" s="14" t="n">
         <v>3616.92</v>
       </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H86" s="8">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H86">
         <f>IF(G86="Overdue",DATE(2026,10,1)-E86,0)</f>
         <v/>
       </c>
@@ -4087,13 +4067,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D87" s="11" t="n">
+      <c r="D87" s="13" t="n">
         <v>46186</v>
       </c>
-      <c r="E87" s="11" t="n">
+      <c r="E87" s="13" t="n">
         <v>46216</v>
       </c>
-      <c r="F87" s="12" t="n">
+      <c r="F87" s="14" t="n">
         <v>1016.99</v>
       </c>
       <c r="G87" t="inlineStr">
@@ -4107,36 +4087,36 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>INV-2026-087</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Eta Pharma</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D88" s="9" t="n">
+      <c r="D88" s="13" t="n">
         <v>46281</v>
       </c>
-      <c r="E88" s="9" t="n">
+      <c r="E88" s="13" t="n">
         <v>46311</v>
       </c>
-      <c r="F88" s="10" t="n">
+      <c r="F88" s="14" t="n">
         <v>531.55</v>
       </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H88" s="8">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H88">
         <f>IF(G88="Overdue",DATE(2026,10,1)-E88,0)</f>
         <v/>
       </c>
@@ -4157,13 +4137,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D89" s="11" t="n">
+      <c r="D89" s="13" t="n">
         <v>46132</v>
       </c>
-      <c r="E89" s="11" t="n">
+      <c r="E89" s="13" t="n">
         <v>46162</v>
       </c>
-      <c r="F89" s="12" t="n">
+      <c r="F89" s="14" t="n">
         <v>379.67</v>
       </c>
       <c r="G89" t="inlineStr">
@@ -4177,36 +4157,36 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>INV-2026-089</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Gamma Retail</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D90" s="9" t="n">
+      <c r="D90" s="13" t="n">
         <v>46279</v>
       </c>
-      <c r="E90" s="9" t="n">
+      <c r="E90" s="13" t="n">
         <v>46309</v>
       </c>
-      <c r="F90" s="10" t="n">
+      <c r="F90" s="14" t="n">
         <v>3218.83</v>
       </c>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H90" s="8">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H90">
         <f>IF(G90="Overdue",DATE(2026,10,1)-E90,0)</f>
         <v/>
       </c>
@@ -4227,13 +4207,13 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D91" s="11" t="n">
+      <c r="D91" s="13" t="n">
         <v>46075</v>
       </c>
-      <c r="E91" s="11" t="n">
+      <c r="E91" s="13" t="n">
         <v>46105</v>
       </c>
-      <c r="F91" s="12" t="n">
+      <c r="F91" s="14" t="n">
         <v>868.86</v>
       </c>
       <c r="G91" t="inlineStr">
@@ -4247,36 +4227,36 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>INV-2026-091</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Alfa Construct</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D92" s="9" t="n">
+      <c r="D92" s="13" t="n">
         <v>46027</v>
       </c>
-      <c r="E92" s="9" t="n">
+      <c r="E92" s="13" t="n">
         <v>46057</v>
       </c>
-      <c r="F92" s="10" t="n">
+      <c r="F92" s="14" t="n">
         <v>3564.55</v>
       </c>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H92" s="8">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H92">
         <f>IF(G92="Overdue",DATE(2026,10,1)-E92,0)</f>
         <v/>
       </c>
@@ -4297,13 +4277,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D93" s="11" t="n">
+      <c r="D93" s="13" t="n">
         <v>46028</v>
       </c>
-      <c r="E93" s="11" t="n">
+      <c r="E93" s="13" t="n">
         <v>46058</v>
       </c>
-      <c r="F93" s="12" t="n">
+      <c r="F93" s="14" t="n">
         <v>3259.49</v>
       </c>
       <c r="G93" t="inlineStr">
@@ -4317,36 +4297,36 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>INV-2026-093</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Delta Foods</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D94" s="9" t="n">
+      <c r="D94" s="13" t="n">
         <v>46214</v>
       </c>
-      <c r="E94" s="9" t="n">
+      <c r="E94" s="13" t="n">
         <v>46244</v>
       </c>
-      <c r="F94" s="10" t="n">
+      <c r="F94" s="14" t="n">
         <v>2698.37</v>
       </c>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H94" s="8">
+      <c r="H94">
         <f>IF(G94="Overdue",DATE(2026,10,1)-E94,0)</f>
         <v/>
       </c>
@@ -4367,13 +4347,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D95" s="11" t="n">
+      <c r="D95" s="13" t="n">
         <v>46046</v>
       </c>
-      <c r="E95" s="11" t="n">
+      <c r="E95" s="13" t="n">
         <v>46076</v>
       </c>
-      <c r="F95" s="12" t="n">
+      <c r="F95" s="14" t="n">
         <v>4440.98</v>
       </c>
       <c r="G95" t="inlineStr">
@@ -4387,36 +4367,36 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>INV-2026-095</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D96" s="9" t="n">
+      <c r="D96" s="13" t="n">
         <v>46028</v>
       </c>
-      <c r="E96" s="9" t="n">
+      <c r="E96" s="13" t="n">
         <v>46058</v>
       </c>
-      <c r="F96" s="10" t="n">
+      <c r="F96" s="14" t="n">
         <v>2493.74</v>
       </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H96" s="8">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H96">
         <f>IF(G96="Overdue",DATE(2026,10,1)-E96,0)</f>
         <v/>
       </c>
@@ -4437,13 +4417,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D97" s="11" t="n">
+      <c r="D97" s="13" t="n">
         <v>46289</v>
       </c>
-      <c r="E97" s="11" t="n">
+      <c r="E97" s="13" t="n">
         <v>46319</v>
       </c>
-      <c r="F97" s="12" t="n">
+      <c r="F97" s="14" t="n">
         <v>1998.85</v>
       </c>
       <c r="G97" t="inlineStr">
@@ -4457,36 +4437,36 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>INV-2026-097</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D98" s="9" t="n">
+      <c r="D98" s="13" t="n">
         <v>46109</v>
       </c>
-      <c r="E98" s="9" t="n">
+      <c r="E98" s="13" t="n">
         <v>46139</v>
       </c>
-      <c r="F98" s="10" t="n">
+      <c r="F98" s="14" t="n">
         <v>2625.2</v>
       </c>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H98" s="8">
+      <c r="H98">
         <f>IF(G98="Overdue",DATE(2026,10,1)-E98,0)</f>
         <v/>
       </c>
@@ -4507,13 +4487,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D99" s="11" t="n">
+      <c r="D99" s="13" t="n">
         <v>46035</v>
       </c>
-      <c r="E99" s="11" t="n">
+      <c r="E99" s="13" t="n">
         <v>46065</v>
       </c>
-      <c r="F99" s="12" t="n">
+      <c r="F99" s="14" t="n">
         <v>3535.17</v>
       </c>
       <c r="G99" t="inlineStr">
@@ -4527,36 +4507,36 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>INV-2026-099</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D100" s="9" t="n">
+      <c r="D100" s="13" t="n">
         <v>46215</v>
       </c>
-      <c r="E100" s="9" t="n">
+      <c r="E100" s="13" t="n">
         <v>46245</v>
       </c>
-      <c r="F100" s="10" t="n">
+      <c r="F100" s="14" t="n">
         <v>3763.93</v>
       </c>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H100" s="8">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H100">
         <f>IF(G100="Overdue",DATE(2026,10,1)-E100,0)</f>
         <v/>
       </c>
@@ -4577,13 +4557,13 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D101" s="11" t="n">
+      <c r="D101" s="13" t="n">
         <v>46275</v>
       </c>
-      <c r="E101" s="11" t="n">
+      <c r="E101" s="13" t="n">
         <v>46305</v>
       </c>
-      <c r="F101" s="12" t="n">
+      <c r="F101" s="14" t="n">
         <v>1015.11</v>
       </c>
       <c r="G101" t="inlineStr">
@@ -4597,36 +4577,36 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>INV-2026-101</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D102" s="9" t="n">
+      <c r="D102" s="13" t="n">
         <v>46092</v>
       </c>
-      <c r="E102" s="9" t="n">
+      <c r="E102" s="13" t="n">
         <v>46122</v>
       </c>
-      <c r="F102" s="10" t="n">
+      <c r="F102" s="14" t="n">
         <v>3722.6</v>
       </c>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H102" s="8">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H102">
         <f>IF(G102="Overdue",DATE(2026,10,1)-E102,0)</f>
         <v/>
       </c>
@@ -4647,13 +4627,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D103" s="11" t="n">
+      <c r="D103" s="13" t="n">
         <v>46116</v>
       </c>
-      <c r="E103" s="11" t="n">
+      <c r="E103" s="13" t="n">
         <v>46146</v>
       </c>
-      <c r="F103" s="12" t="n">
+      <c r="F103" s="14" t="n">
         <v>3393.59</v>
       </c>
       <c r="G103" t="inlineStr">
@@ -4667,36 +4647,36 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>INV-2026-103</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Eta Pharma</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D104" s="9" t="n">
+      <c r="D104" s="13" t="n">
         <v>46213</v>
       </c>
-      <c r="E104" s="9" t="n">
+      <c r="E104" s="13" t="n">
         <v>46243</v>
       </c>
-      <c r="F104" s="10" t="n">
+      <c r="F104" s="14" t="n">
         <v>4927.95</v>
       </c>
-      <c r="G104" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H104" s="8">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H104">
         <f>IF(G104="Overdue",DATE(2026,10,1)-E104,0)</f>
         <v/>
       </c>
@@ -4717,13 +4697,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="13" t="n">
         <v>46208</v>
       </c>
-      <c r="E105" s="11" t="n">
+      <c r="E105" s="13" t="n">
         <v>46238</v>
       </c>
-      <c r="F105" s="12" t="n">
+      <c r="F105" s="14" t="n">
         <v>4269.43</v>
       </c>
       <c r="G105" t="inlineStr">
@@ -4737,36 +4717,36 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>INV-2026-105</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D106" s="9" t="n">
+      <c r="D106" s="13" t="n">
         <v>46138</v>
       </c>
-      <c r="E106" s="9" t="n">
+      <c r="E106" s="13" t="n">
         <v>46168</v>
       </c>
-      <c r="F106" s="10" t="n">
+      <c r="F106" s="14" t="n">
         <v>3801.41</v>
       </c>
-      <c r="G106" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H106" s="8">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H106">
         <f>IF(G106="Overdue",DATE(2026,10,1)-E106,0)</f>
         <v/>
       </c>
@@ -4787,13 +4767,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D107" s="11" t="n">
+      <c r="D107" s="13" t="n">
         <v>46124</v>
       </c>
-      <c r="E107" s="11" t="n">
+      <c r="E107" s="13" t="n">
         <v>46154</v>
       </c>
-      <c r="F107" s="12" t="n">
+      <c r="F107" s="14" t="n">
         <v>1542.18</v>
       </c>
       <c r="G107" t="inlineStr">
@@ -4807,36 +4787,36 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>INV-2026-107</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D108" s="9" t="n">
+      <c r="D108" s="13" t="n">
         <v>46224</v>
       </c>
-      <c r="E108" s="9" t="n">
+      <c r="E108" s="13" t="n">
         <v>46254</v>
       </c>
-      <c r="F108" s="10" t="n">
+      <c r="F108" s="14" t="n">
         <v>4182.4</v>
       </c>
-      <c r="G108" s="8" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="H108" s="8">
+      <c r="H108">
         <f>IF(G108="Overdue",DATE(2026,10,1)-E108,0)</f>
         <v/>
       </c>
@@ -4857,13 +4837,13 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D109" s="13" t="n">
         <v>46150</v>
       </c>
-      <c r="E109" s="11" t="n">
+      <c r="E109" s="13" t="n">
         <v>46180</v>
       </c>
-      <c r="F109" s="12" t="n">
+      <c r="F109" s="14" t="n">
         <v>3525.67</v>
       </c>
       <c r="G109" t="inlineStr">
@@ -4877,36 +4857,36 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>INV-2026-109</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Epsilon Tech</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D110" s="9" t="n">
+      <c r="D110" s="13" t="n">
         <v>46059</v>
       </c>
-      <c r="E110" s="9" t="n">
+      <c r="E110" s="13" t="n">
         <v>46089</v>
       </c>
-      <c r="F110" s="10" t="n">
+      <c r="F110" s="14" t="n">
         <v>1762.23</v>
       </c>
-      <c r="G110" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H110" s="8">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H110">
         <f>IF(G110="Overdue",DATE(2026,10,1)-E110,0)</f>
         <v/>
       </c>
@@ -4927,13 +4907,13 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D111" s="11" t="n">
+      <c r="D111" s="13" t="n">
         <v>46079</v>
       </c>
-      <c r="E111" s="11" t="n">
+      <c r="E111" s="13" t="n">
         <v>46109</v>
       </c>
-      <c r="F111" s="12" t="n">
+      <c r="F111" s="14" t="n">
         <v>2763.63</v>
       </c>
       <c r="G111" t="inlineStr">
@@ -4947,36 +4927,36 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>INV-2026-111</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Beta Media</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D112" s="9" t="n">
+      <c r="D112" s="13" t="n">
         <v>46231</v>
       </c>
-      <c r="E112" s="9" t="n">
+      <c r="E112" s="13" t="n">
         <v>46261</v>
       </c>
-      <c r="F112" s="10" t="n">
+      <c r="F112" s="14" t="n">
         <v>3693.42</v>
       </c>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H112" s="8">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H112">
         <f>IF(G112="Overdue",DATE(2026,10,1)-E112,0)</f>
         <v/>
       </c>
@@ -4997,13 +4977,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D113" s="11" t="n">
+      <c r="D113" s="13" t="n">
         <v>46132</v>
       </c>
-      <c r="E113" s="11" t="n">
+      <c r="E113" s="13" t="n">
         <v>46162</v>
       </c>
-      <c r="F113" s="12" t="n">
+      <c r="F113" s="14" t="n">
         <v>572.41</v>
       </c>
       <c r="G113" t="inlineStr">
@@ -5017,36 +4997,36 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>INV-2026-113</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>Zeta Logistics</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D114" s="9" t="n">
+      <c r="D114" s="13" t="n">
         <v>46155</v>
       </c>
-      <c r="E114" s="9" t="n">
+      <c r="E114" s="13" t="n">
         <v>46185</v>
       </c>
-      <c r="F114" s="10" t="n">
+      <c r="F114" s="14" t="n">
         <v>4014.27</v>
       </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H114" s="8">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H114">
         <f>IF(G114="Overdue",DATE(2026,10,1)-E114,0)</f>
         <v/>
       </c>
@@ -5067,13 +5047,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D115" s="11" t="n">
+      <c r="D115" s="13" t="n">
         <v>46137</v>
       </c>
-      <c r="E115" s="11" t="n">
+      <c r="E115" s="13" t="n">
         <v>46167</v>
       </c>
-      <c r="F115" s="12" t="n">
+      <c r="F115" s="14" t="n">
         <v>3771.92</v>
       </c>
       <c r="G115" t="inlineStr">
@@ -5087,36 +5067,36 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>INV-2026-115</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Theta Style</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D116" s="9" t="n">
+      <c r="D116" s="13" t="n">
         <v>46095</v>
       </c>
-      <c r="E116" s="9" t="n">
+      <c r="E116" s="13" t="n">
         <v>46125</v>
       </c>
-      <c r="F116" s="10" t="n">
+      <c r="F116" s="14" t="n">
         <v>4571.93</v>
       </c>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H116" s="8">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H116">
         <f>IF(G116="Overdue",DATE(2026,10,1)-E116,0)</f>
         <v/>
       </c>
@@ -5137,13 +5117,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D117" s="11" t="n">
+      <c r="D117" s="13" t="n">
         <v>46178</v>
       </c>
-      <c r="E117" s="11" t="n">
+      <c r="E117" s="13" t="n">
         <v>46208</v>
       </c>
-      <c r="F117" s="12" t="n">
+      <c r="F117" s="14" t="n">
         <v>465.33</v>
       </c>
       <c r="G117" t="inlineStr">
@@ -5157,36 +5137,36 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>INV-2026-117</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Alfa Construct</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D118" s="9" t="n">
+      <c r="D118" s="13" t="n">
         <v>46032</v>
       </c>
-      <c r="E118" s="9" t="n">
+      <c r="E118" s="13" t="n">
         <v>46062</v>
       </c>
-      <c r="F118" s="10" t="n">
+      <c r="F118" s="14" t="n">
         <v>4858.8</v>
       </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H118" s="8">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H118">
         <f>IF(G118="Overdue",DATE(2026,10,1)-E118,0)</f>
         <v/>
       </c>
@@ -5207,13 +5187,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D119" s="11" t="n">
+      <c r="D119" s="13" t="n">
         <v>46217</v>
       </c>
-      <c r="E119" s="11" t="n">
+      <c r="E119" s="13" t="n">
         <v>46247</v>
       </c>
-      <c r="F119" s="12" t="n">
+      <c r="F119" s="14" t="n">
         <v>2852.51</v>
       </c>
       <c r="G119" t="inlineStr">
@@ -5227,36 +5207,36 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>INV-2026-119</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Eta Pharma</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D120" s="9" t="n">
+      <c r="D120" s="13" t="n">
         <v>46215</v>
       </c>
-      <c r="E120" s="9" t="n">
+      <c r="E120" s="13" t="n">
         <v>46245</v>
       </c>
-      <c r="F120" s="10" t="n">
+      <c r="F120" s="14" t="n">
         <v>463.4</v>
       </c>
-      <c r="G120" s="8" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="H120" s="8">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="H120">
         <f>IF(G120="Overdue",DATE(2026,10,1)-E120,0)</f>
         <v/>
       </c>
@@ -5277,13 +5257,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D121" s="11" t="n">
+      <c r="D121" s="13" t="n">
         <v>46205</v>
       </c>
-      <c r="E121" s="11" t="n">
+      <c r="E121" s="13" t="n">
         <v>46235</v>
       </c>
-      <c r="F121" s="12" t="n">
+      <c r="F121" s="14" t="n">
         <v>2422.8</v>
       </c>
       <c r="G121" t="inlineStr">
@@ -5298,6 +5278,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H121"/>
+  <conditionalFormatting sqref="G2:G121">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Paid"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Overdue"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Pending"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5308,7 +5299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5352,6 +5343,16 @@
           <t>Invoices</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5390,6 +5391,15 @@
         <f>COUNTIF(Data!$G$2:$G$121,J2)</f>
         <v/>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1-30 days</t>
+        </is>
+      </c>
+      <c r="N2">
+        <f>SUMIFS(Data!$F$2:$F$121,Data!$H$2:$H$121,"&gt;=1",Data!$H$2:$H$121,"&lt;=30")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5428,6 +5438,15 @@
         <f>COUNTIF(Data!$G$2:$G$121,J3)</f>
         <v/>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>31-60 days</t>
+        </is>
+      </c>
+      <c r="N3">
+        <f>SUMIFS(Data!$F$2:$F$121,Data!$H$2:$H$121,"&gt;=1",Data!$H$2:$H$121,"&lt;=30")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5466,6 +5485,15 @@
         <f>COUNTIF(Data!$G$2:$G$121,J4)</f>
         <v/>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>61-90 days</t>
+        </is>
+      </c>
+      <c r="N4">
+        <f>SUMIFS(Data!$F$2:$F$121,Data!$H$2:$H$121,"&gt;=1",Data!$H$2:$H$121,"&lt;=30")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="D5" t="inlineStr">
@@ -5486,6 +5514,14 @@
         <f>SUMIFS(Data!$F$2:$F$121,Data!$B$2:$B$121,G5,Data!$G$2:$G$121,"&lt;&gt;Paid")</f>
         <v/>
       </c>
+      <c r="M5">
+        <f>SUMIFS(Data!$F$2:$F$121,Data!$H$2:$H$121,"&gt;=31",Data!$H$2:$H$121,"&lt;=60")</f>
+        <v/>
+      </c>
+      <c r="N5">
+        <f>SUMIFS(Data!$F$2:$F$121,Data!$H$2:$H$121,"&gt;=1",Data!$H$2:$H$121,"&lt;=30")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="D6" t="inlineStr">
@@ -5506,6 +5542,10 @@
         <f>SUMIFS(Data!$F$2:$F$121,Data!$B$2:$B$121,G6,Data!$G$2:$G$121,"&lt;&gt;Paid")</f>
         <v/>
       </c>
+      <c r="M6">
+        <f>SUMIFS(Data!$F$2:$F$121,Data!$H$2:$H$121,"&gt;=61",Data!$H$2:$H$121,"&lt;=90")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="D7" t="inlineStr">
@@ -5524,6 +5564,10 @@
       </c>
       <c r="H7">
         <f>SUMIFS(Data!$F$2:$F$121,Data!$B$2:$B$121,G7,Data!$G$2:$G$121,"&lt;&gt;Paid")</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>SUMIFS(Data!$F$2:$F$121,Data!$H$2:$H$121,"&gt;=91")</f>
         <v/>
       </c>
     </row>
